--- a/diseases/d106/2000-2004.xlsx
+++ b/diseases/d106/2000-2004.xlsx
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN8" t="b">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN38" t="b">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14775,7 +14775,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16683,7 +16683,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17637,7 +17637,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19545,7 +19545,7 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN100" t="b">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -24315,7 +24315,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25672,7 +25672,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -26626,7 +26626,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27580,7 +27580,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29488,7 +29488,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -30442,7 +30442,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31396,7 +31396,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -32350,7 +32350,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33304,7 +33304,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -34258,7 +34258,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35212,7 +35212,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN194" t="b">
@@ -38477,7 +38477,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39431,7 +39431,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -40385,7 +40385,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41339,7 +41339,7 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN214" t="b">
@@ -42293,7 +42293,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -43247,7 +43247,7 @@
       </c>
       <c r="AM224" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN224" t="b">
@@ -44201,7 +44201,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45155,7 +45155,7 @@
       </c>
       <c r="AM234" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN234" t="b">
@@ -46109,7 +46109,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -47063,7 +47063,7 @@
       </c>
       <c r="AM244" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN244" t="b">
@@ -48017,7 +48017,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -49374,7 +49374,7 @@
       </c>
       <c r="AM256" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN256" t="b">
@@ -50328,7 +50328,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51282,7 +51282,7 @@
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN266" t="b">
@@ -52236,7 +52236,7 @@
       </c>
       <c r="AM271" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN271" t="b">
@@ -53190,7 +53190,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -54144,7 +54144,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -55098,7 +55098,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -56052,7 +56052,7 @@
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -57006,7 +57006,7 @@
       </c>
       <c r="AM296" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN296" t="b">
@@ -57960,7 +57960,7 @@
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -58914,7 +58914,7 @@
       </c>
       <c r="AM306" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN306" t="b">
@@ -59868,7 +59868,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
